--- a/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
+++ b/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/CRbQ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE139A42-4913-6D4C-891D-6F30696E1BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8319EDF8-0ABD-564B-8546-22DD33F30EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BCRBQ_IDN" sheetId="2" r:id="rId2"/>
-    <sheet name="CRbQ" sheetId="3" r:id="rId3"/>
+    <sheet name="BCRbQ" sheetId="4" r:id="rId3"/>
+    <sheet name="CRbQ" sheetId="3" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
   <si>
     <t>CRbQ Capacity Retirements before Quantization</t>
   </si>
@@ -164,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +189,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -218,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -238,6 +250,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -253,6 +270,67 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="coal retirement"/>
+      <sheetName val="Computation"/>
+      <sheetName val="BCRbQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="B2">
+            <v>157.14285714285714</v>
+          </cell>
+          <cell r="C2">
+            <v>157.14285714285714</v>
+          </cell>
+          <cell r="D2">
+            <v>157.14285714285714</v>
+          </cell>
+          <cell r="E2">
+            <v>157.14285714285714</v>
+          </cell>
+          <cell r="F2">
+            <v>157.14285714285714</v>
+          </cell>
+          <cell r="G2">
+            <v>157.14285714285714</v>
+          </cell>
+          <cell r="H2">
+            <v>157.14285714285714</v>
+          </cell>
+          <cell r="I2">
+            <v>200</v>
+          </cell>
+          <cell r="J2">
+            <v>200</v>
+          </cell>
+          <cell r="K2">
+            <v>200</v>
+          </cell>
+          <cell r="L2">
+            <v>200</v>
+          </cell>
+          <cell r="M2">
+            <v>200</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3398,6 +3476,2926 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{556013AF-EC51-F841-A600-B92BB7D8ABAE}">
+  <dimension ref="A1:BA18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:53" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="13">
+        <v>2019</v>
+      </c>
+      <c r="C1" s="13">
+        <v>2020</v>
+      </c>
+      <c r="D1" s="13">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="13">
+        <v>2022</v>
+      </c>
+      <c r="F1" s="13">
+        <v>2023</v>
+      </c>
+      <c r="G1" s="13">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="13">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="13">
+        <v>2026</v>
+      </c>
+      <c r="J1" s="13">
+        <v>2027</v>
+      </c>
+      <c r="K1" s="13">
+        <v>2028</v>
+      </c>
+      <c r="L1" s="13">
+        <v>2029</v>
+      </c>
+      <c r="M1" s="13">
+        <v>2030</v>
+      </c>
+      <c r="N1" s="13">
+        <v>2031</v>
+      </c>
+      <c r="O1" s="13">
+        <v>2032</v>
+      </c>
+      <c r="P1" s="13">
+        <v>2033</v>
+      </c>
+      <c r="Q1" s="13">
+        <v>2034</v>
+      </c>
+      <c r="R1" s="13">
+        <v>2035</v>
+      </c>
+      <c r="S1" s="13">
+        <v>2036</v>
+      </c>
+      <c r="T1" s="13">
+        <v>2037</v>
+      </c>
+      <c r="U1" s="13">
+        <v>2038</v>
+      </c>
+      <c r="V1" s="13">
+        <v>2039</v>
+      </c>
+      <c r="W1" s="13">
+        <v>2040</v>
+      </c>
+      <c r="X1" s="13">
+        <v>2041</v>
+      </c>
+      <c r="Y1" s="13">
+        <v>2042</v>
+      </c>
+      <c r="Z1" s="13">
+        <v>2043</v>
+      </c>
+      <c r="AA1" s="13">
+        <v>2044</v>
+      </c>
+      <c r="AB1" s="13">
+        <v>2045</v>
+      </c>
+      <c r="AC1" s="13">
+        <v>2046</v>
+      </c>
+      <c r="AD1" s="13">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="13">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="13">
+        <v>2049</v>
+      </c>
+      <c r="AG1" s="13">
+        <v>2050</v>
+      </c>
+      <c r="AH1" s="14">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="14">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="14">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="14">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="14">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="14">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="14">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="14">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="14">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="14">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="14">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="14">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="14">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="14">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="14">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="14">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="14">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="14">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="14">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="14">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="12">
+        <f>[1]Computation!B2</f>
+        <v>157.14285714285714</v>
+      </c>
+      <c r="C2" s="12">
+        <f>[1]Computation!C2</f>
+        <v>157.14285714285714</v>
+      </c>
+      <c r="D2" s="12">
+        <f>[1]Computation!D2</f>
+        <v>157.14285714285714</v>
+      </c>
+      <c r="E2" s="12">
+        <f>[1]Computation!E2</f>
+        <v>157.14285714285714</v>
+      </c>
+      <c r="F2" s="12">
+        <f>[1]Computation!F2</f>
+        <v>157.14285714285714</v>
+      </c>
+      <c r="G2" s="12">
+        <f>[1]Computation!G2</f>
+        <v>157.14285714285714</v>
+      </c>
+      <c r="H2" s="12">
+        <f>[1]Computation!H2</f>
+        <v>157.14285714285714</v>
+      </c>
+      <c r="I2" s="12">
+        <f>[1]Computation!I2</f>
+        <v>200</v>
+      </c>
+      <c r="J2" s="12">
+        <f>[1]Computation!J2</f>
+        <v>200</v>
+      </c>
+      <c r="K2" s="12">
+        <f>[1]Computation!K2</f>
+        <v>200</v>
+      </c>
+      <c r="L2" s="12">
+        <f>[1]Computation!L2</f>
+        <v>200</v>
+      </c>
+      <c r="M2" s="12">
+        <f>[1]Computation!M2</f>
+        <v>200</v>
+      </c>
+      <c r="N2" s="12">
+        <v>0</v>
+      </c>
+      <c r="O2" s="12">
+        <v>0</v>
+      </c>
+      <c r="P2" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="12">
+        <v>0</v>
+      </c>
+      <c r="R2" s="12">
+        <v>0</v>
+      </c>
+      <c r="S2" s="12">
+        <v>0</v>
+      </c>
+      <c r="T2" s="12">
+        <v>0</v>
+      </c>
+      <c r="U2" s="12">
+        <v>0</v>
+      </c>
+      <c r="V2" s="12">
+        <v>0</v>
+      </c>
+      <c r="W2" s="12">
+        <v>0</v>
+      </c>
+      <c r="X2" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA2" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="12">
+        <v>0</v>
+      </c>
+      <c r="C3" s="12">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12">
+        <v>0</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0</v>
+      </c>
+      <c r="K3" s="12">
+        <v>0</v>
+      </c>
+      <c r="L3" s="12">
+        <v>0</v>
+      </c>
+      <c r="M3" s="12">
+        <v>0</v>
+      </c>
+      <c r="N3" s="12">
+        <v>0</v>
+      </c>
+      <c r="O3" s="12">
+        <v>0</v>
+      </c>
+      <c r="P3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>0</v>
+      </c>
+      <c r="R3" s="12">
+        <v>0</v>
+      </c>
+      <c r="S3" s="12">
+        <v>0</v>
+      </c>
+      <c r="T3" s="12">
+        <v>0</v>
+      </c>
+      <c r="U3" s="12">
+        <v>0</v>
+      </c>
+      <c r="V3" s="12">
+        <v>0</v>
+      </c>
+      <c r="W3" s="12">
+        <v>0</v>
+      </c>
+      <c r="X3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA3" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="12">
+        <v>0</v>
+      </c>
+      <c r="C4" s="12">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12">
+        <v>0</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0</v>
+      </c>
+      <c r="K4" s="12">
+        <v>0</v>
+      </c>
+      <c r="L4" s="12">
+        <v>0</v>
+      </c>
+      <c r="M4" s="12">
+        <v>0</v>
+      </c>
+      <c r="N4" s="12">
+        <v>0</v>
+      </c>
+      <c r="O4" s="12">
+        <v>0</v>
+      </c>
+      <c r="P4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>0</v>
+      </c>
+      <c r="R4" s="12">
+        <v>0</v>
+      </c>
+      <c r="S4" s="12">
+        <v>0</v>
+      </c>
+      <c r="T4" s="12">
+        <v>0</v>
+      </c>
+      <c r="U4" s="12">
+        <v>0</v>
+      </c>
+      <c r="V4" s="12">
+        <v>0</v>
+      </c>
+      <c r="W4" s="12">
+        <v>0</v>
+      </c>
+      <c r="X4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA4" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="12">
+        <v>0</v>
+      </c>
+      <c r="C5" s="12">
+        <v>0</v>
+      </c>
+      <c r="D5" s="12">
+        <v>0</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0</v>
+      </c>
+      <c r="I5" s="12">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12">
+        <v>0</v>
+      </c>
+      <c r="K5" s="12">
+        <v>0</v>
+      </c>
+      <c r="L5" s="12">
+        <v>0</v>
+      </c>
+      <c r="M5" s="12">
+        <v>0</v>
+      </c>
+      <c r="N5" s="12">
+        <v>0</v>
+      </c>
+      <c r="O5" s="12">
+        <v>0</v>
+      </c>
+      <c r="P5" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>0</v>
+      </c>
+      <c r="R5" s="12">
+        <v>0</v>
+      </c>
+      <c r="S5" s="12">
+        <v>0</v>
+      </c>
+      <c r="T5" s="12">
+        <v>0</v>
+      </c>
+      <c r="U5" s="12">
+        <v>0</v>
+      </c>
+      <c r="V5" s="12">
+        <v>0</v>
+      </c>
+      <c r="W5" s="12">
+        <v>0</v>
+      </c>
+      <c r="X5" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY5" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="12">
+        <v>0</v>
+      </c>
+      <c r="C6" s="12">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0</v>
+      </c>
+      <c r="K6" s="12">
+        <v>0</v>
+      </c>
+      <c r="L6" s="12">
+        <v>0</v>
+      </c>
+      <c r="M6" s="12">
+        <v>0</v>
+      </c>
+      <c r="N6" s="12">
+        <v>0</v>
+      </c>
+      <c r="O6" s="12">
+        <v>0</v>
+      </c>
+      <c r="P6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>0</v>
+      </c>
+      <c r="R6" s="12">
+        <v>0</v>
+      </c>
+      <c r="S6" s="12">
+        <v>0</v>
+      </c>
+      <c r="T6" s="12">
+        <v>0</v>
+      </c>
+      <c r="U6" s="12">
+        <v>0</v>
+      </c>
+      <c r="V6" s="12">
+        <v>0</v>
+      </c>
+      <c r="W6" s="12">
+        <v>0</v>
+      </c>
+      <c r="X6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA6" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="12">
+        <v>0</v>
+      </c>
+      <c r="C7" s="12">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0</v>
+      </c>
+      <c r="J7" s="12">
+        <v>0</v>
+      </c>
+      <c r="K7" s="12">
+        <v>0</v>
+      </c>
+      <c r="L7" s="12">
+        <v>0</v>
+      </c>
+      <c r="M7" s="12">
+        <v>0</v>
+      </c>
+      <c r="N7" s="12">
+        <v>0</v>
+      </c>
+      <c r="O7" s="12">
+        <v>0</v>
+      </c>
+      <c r="P7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="12">
+        <v>0</v>
+      </c>
+      <c r="R7" s="12">
+        <v>0</v>
+      </c>
+      <c r="S7" s="12">
+        <v>0</v>
+      </c>
+      <c r="T7" s="12">
+        <v>0</v>
+      </c>
+      <c r="U7" s="12">
+        <v>0</v>
+      </c>
+      <c r="V7" s="12">
+        <v>0</v>
+      </c>
+      <c r="W7" s="12">
+        <v>0</v>
+      </c>
+      <c r="X7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA7" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="12">
+        <v>0</v>
+      </c>
+      <c r="C8" s="12">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0</v>
+      </c>
+      <c r="K8" s="12">
+        <v>0</v>
+      </c>
+      <c r="L8" s="12">
+        <v>0</v>
+      </c>
+      <c r="M8" s="12">
+        <v>0</v>
+      </c>
+      <c r="N8" s="12">
+        <v>0</v>
+      </c>
+      <c r="O8" s="12">
+        <v>0</v>
+      </c>
+      <c r="P8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>0</v>
+      </c>
+      <c r="R8" s="12">
+        <v>0</v>
+      </c>
+      <c r="S8" s="12">
+        <v>0</v>
+      </c>
+      <c r="T8" s="12">
+        <v>0</v>
+      </c>
+      <c r="U8" s="12">
+        <v>0</v>
+      </c>
+      <c r="V8" s="12">
+        <v>0</v>
+      </c>
+      <c r="W8" s="12">
+        <v>0</v>
+      </c>
+      <c r="X8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="12">
+        <v>0</v>
+      </c>
+      <c r="C9" s="12">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0</v>
+      </c>
+      <c r="K9" s="12">
+        <v>0</v>
+      </c>
+      <c r="L9" s="12">
+        <v>0</v>
+      </c>
+      <c r="M9" s="12">
+        <v>0</v>
+      </c>
+      <c r="N9" s="12">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12">
+        <v>0</v>
+      </c>
+      <c r="P9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12">
+        <v>0</v>
+      </c>
+      <c r="S9" s="12">
+        <v>0</v>
+      </c>
+      <c r="T9" s="12">
+        <v>0</v>
+      </c>
+      <c r="U9" s="12">
+        <v>0</v>
+      </c>
+      <c r="V9" s="12">
+        <v>0</v>
+      </c>
+      <c r="W9" s="12">
+        <v>0</v>
+      </c>
+      <c r="X9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA9" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="12">
+        <v>0</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0</v>
+      </c>
+      <c r="K10" s="12">
+        <v>0</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
+        <v>0</v>
+      </c>
+      <c r="N10" s="12">
+        <v>0</v>
+      </c>
+      <c r="O10" s="12">
+        <v>0</v>
+      </c>
+      <c r="P10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>0</v>
+      </c>
+      <c r="R10" s="12">
+        <v>0</v>
+      </c>
+      <c r="S10" s="12">
+        <v>0</v>
+      </c>
+      <c r="T10" s="12">
+        <v>0</v>
+      </c>
+      <c r="U10" s="12">
+        <v>0</v>
+      </c>
+      <c r="V10" s="12">
+        <v>0</v>
+      </c>
+      <c r="W10" s="12">
+        <v>0</v>
+      </c>
+      <c r="X10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA10" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="12">
+        <v>0</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0</v>
+      </c>
+      <c r="J11" s="12">
+        <v>0</v>
+      </c>
+      <c r="K11" s="12">
+        <v>0</v>
+      </c>
+      <c r="L11" s="12">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12">
+        <v>0</v>
+      </c>
+      <c r="N11" s="12">
+        <v>0</v>
+      </c>
+      <c r="O11" s="12">
+        <v>0</v>
+      </c>
+      <c r="P11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="12">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12">
+        <v>0</v>
+      </c>
+      <c r="S11" s="12">
+        <v>0</v>
+      </c>
+      <c r="T11" s="12">
+        <v>0</v>
+      </c>
+      <c r="U11" s="12">
+        <v>0</v>
+      </c>
+      <c r="V11" s="12">
+        <v>0</v>
+      </c>
+      <c r="W11" s="12">
+        <v>0</v>
+      </c>
+      <c r="X11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA11" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="12">
+        <v>0</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="12">
+        <v>0</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12">
+        <v>0</v>
+      </c>
+      <c r="O12" s="12">
+        <v>0</v>
+      </c>
+      <c r="P12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0</v>
+      </c>
+      <c r="R12" s="12">
+        <v>0</v>
+      </c>
+      <c r="S12" s="12">
+        <v>0</v>
+      </c>
+      <c r="T12" s="12">
+        <v>0</v>
+      </c>
+      <c r="U12" s="12">
+        <v>0</v>
+      </c>
+      <c r="V12" s="12">
+        <v>0</v>
+      </c>
+      <c r="W12" s="12">
+        <v>0</v>
+      </c>
+      <c r="X12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="12">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0</v>
+      </c>
+      <c r="K13" s="12">
+        <v>0</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0</v>
+      </c>
+      <c r="M13" s="12">
+        <v>0</v>
+      </c>
+      <c r="N13" s="12">
+        <v>0</v>
+      </c>
+      <c r="O13" s="12">
+        <v>0</v>
+      </c>
+      <c r="P13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>0</v>
+      </c>
+      <c r="R13" s="12">
+        <v>0</v>
+      </c>
+      <c r="S13" s="12">
+        <v>0</v>
+      </c>
+      <c r="T13" s="12">
+        <v>0</v>
+      </c>
+      <c r="U13" s="12">
+        <v>0</v>
+      </c>
+      <c r="V13" s="12">
+        <v>0</v>
+      </c>
+      <c r="W13" s="12">
+        <v>0</v>
+      </c>
+      <c r="X13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="12">
+        <v>0</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12">
+        <v>0</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0</v>
+      </c>
+      <c r="I14" s="12">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12">
+        <v>0</v>
+      </c>
+      <c r="K14" s="12">
+        <v>0</v>
+      </c>
+      <c r="L14" s="12">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12">
+        <v>0</v>
+      </c>
+      <c r="N14" s="12">
+        <v>0</v>
+      </c>
+      <c r="O14" s="12">
+        <v>0</v>
+      </c>
+      <c r="P14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>0</v>
+      </c>
+      <c r="R14" s="12">
+        <v>0</v>
+      </c>
+      <c r="S14" s="12">
+        <v>0</v>
+      </c>
+      <c r="T14" s="12">
+        <v>0</v>
+      </c>
+      <c r="U14" s="12">
+        <v>0</v>
+      </c>
+      <c r="V14" s="12">
+        <v>0</v>
+      </c>
+      <c r="W14" s="12">
+        <v>0</v>
+      </c>
+      <c r="X14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="12">
+        <v>0</v>
+      </c>
+      <c r="C15" s="12">
+        <v>0</v>
+      </c>
+      <c r="D15" s="12">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12">
+        <v>0</v>
+      </c>
+      <c r="K15" s="12">
+        <v>0</v>
+      </c>
+      <c r="L15" s="12">
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
+        <v>0</v>
+      </c>
+      <c r="N15" s="12">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12">
+        <v>0</v>
+      </c>
+      <c r="P15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>0</v>
+      </c>
+      <c r="R15" s="12">
+        <v>0</v>
+      </c>
+      <c r="S15" s="12">
+        <v>0</v>
+      </c>
+      <c r="T15" s="12">
+        <v>0</v>
+      </c>
+      <c r="U15" s="12">
+        <v>0</v>
+      </c>
+      <c r="V15" s="12">
+        <v>0</v>
+      </c>
+      <c r="W15" s="12">
+        <v>0</v>
+      </c>
+      <c r="X15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="12">
+        <v>0</v>
+      </c>
+      <c r="C16" s="12">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0</v>
+      </c>
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
+      <c r="L16" s="12">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
+        <v>0</v>
+      </c>
+      <c r="N16" s="12">
+        <v>0</v>
+      </c>
+      <c r="O16" s="12">
+        <v>0</v>
+      </c>
+      <c r="P16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="12">
+        <v>0</v>
+      </c>
+      <c r="R16" s="12">
+        <v>0</v>
+      </c>
+      <c r="S16" s="12">
+        <v>0</v>
+      </c>
+      <c r="T16" s="12">
+        <v>0</v>
+      </c>
+      <c r="U16" s="12">
+        <v>0</v>
+      </c>
+      <c r="V16" s="12">
+        <v>0</v>
+      </c>
+      <c r="W16" s="12">
+        <v>0</v>
+      </c>
+      <c r="X16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="12">
+        <v>0</v>
+      </c>
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0</v>
+      </c>
+      <c r="I17" s="12">
+        <v>0</v>
+      </c>
+      <c r="J17" s="12">
+        <v>0</v>
+      </c>
+      <c r="K17" s="12">
+        <v>0</v>
+      </c>
+      <c r="L17" s="12">
+        <v>0</v>
+      </c>
+      <c r="M17" s="12">
+        <v>0</v>
+      </c>
+      <c r="N17" s="12">
+        <v>0</v>
+      </c>
+      <c r="O17" s="12">
+        <v>0</v>
+      </c>
+      <c r="P17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="12">
+        <v>0</v>
+      </c>
+      <c r="R17" s="12">
+        <v>0</v>
+      </c>
+      <c r="S17" s="12">
+        <v>0</v>
+      </c>
+      <c r="T17" s="12">
+        <v>0</v>
+      </c>
+      <c r="U17" s="12">
+        <v>0</v>
+      </c>
+      <c r="V17" s="12">
+        <v>0</v>
+      </c>
+      <c r="W17" s="12">
+        <v>0</v>
+      </c>
+      <c r="X17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="12">
+        <v>0</v>
+      </c>
+      <c r="C18" s="12">
+        <v>0</v>
+      </c>
+      <c r="D18" s="12">
+        <v>0</v>
+      </c>
+      <c r="E18" s="12">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0</v>
+      </c>
+      <c r="I18" s="12">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12">
+        <v>0</v>
+      </c>
+      <c r="K18" s="12">
+        <v>0</v>
+      </c>
+      <c r="L18" s="12">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12">
+        <v>0</v>
+      </c>
+      <c r="N18" s="12">
+        <v>0</v>
+      </c>
+      <c r="O18" s="12">
+        <v>0</v>
+      </c>
+      <c r="P18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>0</v>
+      </c>
+      <c r="R18" s="12">
+        <v>0</v>
+      </c>
+      <c r="S18" s="12">
+        <v>0</v>
+      </c>
+      <c r="T18" s="12">
+        <v>0</v>
+      </c>
+      <c r="U18" s="12">
+        <v>0</v>
+      </c>
+      <c r="V18" s="12">
+        <v>0</v>
+      </c>
+      <c r="W18" s="12">
+        <v>0</v>
+      </c>
+      <c r="X18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="12">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="12">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="12">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1E4E79"/>
@@ -3594,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="10">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="I2" s="10">
         <v>0</v>
@@ -3609,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="10">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="N2" s="10">
         <v>0</v>
@@ -3720,15 +6718,19 @@
         <v>0</v>
       </c>
       <c r="AX2" s="10">
+        <f>BCRbQ!AX2</f>
         <v>0</v>
       </c>
       <c r="AY2" s="10">
+        <f>BCRbQ!AY2</f>
         <v>0</v>
       </c>
       <c r="AZ2" s="10">
+        <f>BCRbQ!AZ2</f>
         <v>0</v>
       </c>
       <c r="BA2" s="10">
+        <f>BCRbQ!BA2</f>
         <v>0</v>
       </c>
     </row>
